--- a/experiments/reports/summary.xlsx
+++ b/experiments/reports/summary.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="abp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="abp_x0.75" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="abp_x1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="abp_x1.25" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="abp_x1.5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="abp_x1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="abp_x1.25" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="abp_x1.5" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,25 +441,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Target value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -490,29 +493,30 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>569.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -537,25 +541,30 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>74.43</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -584,29 +593,30 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>637.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -631,29 +641,30 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>412.7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -678,29 +689,30 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>476.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -725,25 +737,30 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>8.43</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -772,29 +789,30 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>409.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -819,29 +837,30 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>405.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -866,29 +885,30 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>546.7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -913,29 +933,30 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>281.7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -960,29 +981,30 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>180.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.01</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1007,25 +1029,30 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1054,25 +1081,30 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>119.8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>240.1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1097,25 +1129,30 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>239.6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1140,29 +1177,30 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.03</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1187,25 +1225,30 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>192</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>119.1</t>
+          <t>445</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>330.0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1230,29 +1273,30 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>227</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>319.7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.01</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1277,25 +1321,30 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>172.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>302.8</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1320,29 +1369,30 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>261</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>279.3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1367,29 +1417,30 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>213</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>402.4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1414,25 +1465,30 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>662</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>662</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>193.1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
+        <is>
+          <t>70.13</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1461,29 +1517,30 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>329</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>331</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>385.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.03</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1508,25 +1565,30 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>172.1</t>
+          <t>685</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>454.6</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>1800.03</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1551,25 +1613,30 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>181.2</t>
+          <t>715</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>476.3</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1582,7 +1649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1608,25 +1675,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Target value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -1655,29 +1727,30 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>436.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1702,25 +1775,30 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>5.51</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1749,25 +1827,30 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1796,25 +1879,30 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1843,25 +1931,30 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1890,25 +1983,30 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1937,25 +2035,30 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>145.83</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1984,29 +2087,30 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>234.13</t>
+          <t>333.4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2031,29 +2135,30 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>542.9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2078,29 +2183,30 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>299.8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2125,29 +2231,30 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>128</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2172,25 +2279,30 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>145</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2219,25 +2331,30 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>233.4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2262,25 +2379,30 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>132.6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>235.8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2305,29 +2427,30 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>305</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>429.6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.03</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2352,25 +2475,30 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>212</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>139.6</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1800.05</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>308.1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2395,29 +2523,30 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>283</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>570</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>607</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>257.5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2442,25 +2571,30 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>160</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>200.1</t>
+          <t>604</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>312.9</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2485,29 +2619,30 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>326</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>328</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>648</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>265.5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2532,29 +2667,30 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>264</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>633</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>25.47</t>
+          <t>411.1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2579,25 +2715,30 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>275</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>827</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>827</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>191.7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
+        <is>
+          <t>79.05</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2626,29 +2767,30 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>411</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>413</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>803</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>386.4</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2673,25 +2815,30 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>325</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>851</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>387.1</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2716,25 +2863,30 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>145</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>286</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>216.4</t>
+          <t>766</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>410.3</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>1800.06</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2747,7 +2899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,25 +2925,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Target value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -2820,29 +2977,30 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>402.4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2867,25 +3025,30 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>8.81</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2914,25 +3077,30 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2961,25 +3129,30 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>61.67</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3008,25 +3181,30 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3055,25 +3233,30 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3102,25 +3285,30 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>242.45</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3149,29 +3337,30 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1016.95</t>
+          <t>379.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3196,29 +3385,30 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>605.6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3243,29 +3433,30 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>285.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3290,29 +3481,30 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>154</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>136.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3337,25 +3529,30 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>175</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3384,25 +3581,30 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>272.8</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1800.05</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3427,25 +3629,30 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>271.7</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3470,29 +3677,30 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>358</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>594</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>33.92</t>
+          <t>548.9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3517,25 +3725,30 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>143.9</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>437.1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3560,29 +3773,30 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>683</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>719</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>224.3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3607,25 +3821,30 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>190</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>217.4</t>
+          <t>716</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>331.4</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3650,29 +3869,30 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>391</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>393</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>714</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>318.5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3697,29 +3917,30 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>344</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>717</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>443.3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3744,25 +3965,30 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>330</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>992</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>992</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>251.2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
+        <is>
+          <t>197.93</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3791,29 +4017,30 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>493</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>495</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>892</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>419.7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3838,25 +4065,30 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>239.6</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>449.7</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3881,2343 +4113,30 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>343</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>232.7</t>
+          <t>908</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Time limit (s)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Worker count</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Best bound</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Best objective</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Memory consumed (MB)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Time consumed (s)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Optimal found</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A-pores_1.txt</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>A-pores_1.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B-ibm32.txt</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>B-ibm32.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C-bcspwr01.txt</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>C-bcspwr01.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>D-bcsstk01.txt</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>D-bcsstk01.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>14.05</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>E-bcspwr02.txt</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>E-bcspwr02.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>F-curtis54.txt</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>F-curtis54.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>G-will57.txt</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>G-will57.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>H-impcol_b.txt</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>H-impcol_b.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>302.5</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1800.01</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>I-ash85.txt</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>I-ash85.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>J-nos4.txt</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>J-nos4.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>K-dwt__234.txt</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>K-dwt__234.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>L-bcspwr03.txt</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>L-bcspwr03.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>M-bcsstk06.txt</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>M-bcsstk06.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>167.1</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>N-bcsstk07.txt</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>N-bcsstk07.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>167.3</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1800.06</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>O-impcol_d.txt</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>O-impcol_d.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>18.37</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>P-can__445.txt</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>P-can__445.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>163.5</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Q-494_bus.txt</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Q-494_bus.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R-dwt__503.txt</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>R-dwt__503.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>293.7</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1800.05</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>S-sherman4.txt</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S-sherman4.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>T-dwt__592.txt</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>T-dwt__592.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>97.2</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>84.34</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>U-662_bus.txt</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>U-662_bus.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>93.2</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>57.40</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>V-nos6.txt</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>V-nos6.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>W-685_bus.txt</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>W-685_bus.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>242.4</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>X-can__715.txt</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>X-can__715.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>243.8</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+          <t>451.4</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>1800.07</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Time limit (s)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Worker count</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Best bound</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Best objective</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Memory consumed (MB)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Time consumed (s)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Optimal found</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A-pores_1.txt</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>A-pores_1.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B-ibm32.txt</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>B-ibm32.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C-bcspwr01.txt</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>C-bcspwr01.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>D-bcsstk01.txt</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>D-bcsstk01.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>51.45</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>E-bcspwr02.txt</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>E-bcspwr02.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>F-curtis54.txt</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>F-curtis54.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.61</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>G-will57.txt</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>G-will57.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>H-impcol_b.txt</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>H-impcol_b.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>328.6</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>I-ash85.txt</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>I-ash85.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>10.6</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>J-nos4.txt</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>J-nos4.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>K-dwt__234.txt</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>K-dwt__234.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>L-bcspwr03.txt</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>L-bcspwr03.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>M-bcsstk06.txt</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>M-bcsstk06.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>187.7</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1800.06</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>N-bcsstk07.txt</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>N-bcsstk07.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>188.2</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>O-impcol_d.txt</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>O-impcol_d.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>75.4</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>77.82</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>P-can__445.txt</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>P-can__445.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>186.3</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1800.05</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Q-494_bus.txt</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Q-494_bus.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>51.8</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R-dwt__503.txt</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>R-dwt__503.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>359.1</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1800.06</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>S-sherman4.txt</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S-sherman4.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>T-dwt__592.txt</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>T-dwt__592.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>101.93</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>U-662_bus.txt</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>U-662_bus.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>97.6</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>58.70</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>V-nos6.txt</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>V-nos6.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>71.4</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>W-685_bus.txt</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>W-685_bus.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>298.2</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>X-can__715.txt</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>X-can__715.mtx.rnd</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>268.2</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>1800.07</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
